--- a/artfynd/A 19899-2026 artfynd.xlsx
+++ b/artfynd/A 19899-2026 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91281659</v>
+        <v>91281633</v>
       </c>
       <c r="B2" t="n">
-        <v>98681</v>
+        <v>100856</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>1256</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Forselles</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bomhus, Storhagen, Gstr</t>
+          <t>Bomhus, Storhagen 1 km S, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623303</v>
+        <v>623302</v>
       </c>
       <c r="R2" t="n">
-        <v>6727248</v>
+        <v>6727326</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,12 +759,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Skog, blandskog, 40-årig fuktig tallskog m björkunderväxt</t>
+          <t>Källa, källstråk i myr artad tallskog</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 289880N</t>
+          <t>Gst Fyndnr 289906H</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,48 +786,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91281635</v>
+        <v>98181688</v>
       </c>
       <c r="B3" t="n">
-        <v>98682</v>
+        <v>100856</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>1256</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Forselles</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bomhus, Storhagen, Gstr</t>
+          <t>Storhagen, 1 km N om dammen i Storhagen, på fastigh 16:18, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623297</v>
+        <v>623313</v>
       </c>
       <c r="R3" t="n">
-        <v>6727197</v>
+        <v>6727231</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2006-06-03</t>
+          <t>1991-08-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2006-06-03</t>
+          <t>1991-08-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Över 100 blommande strån av storgröe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,12 +875,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Skog, blandskog, 30årig tall med björk, prunkande örtflora</t>
+          <t>Källa, i fuktig gles tallskog på torvmark. Utströmningsområdeför kalkrikt grundvatten.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 289904N</t>
+          <t>Gst Fyndnr 42791H</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91281631</v>
+        <v>91281622</v>
       </c>
       <c r="B4" t="n">
-        <v>105807</v>
+        <v>99142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221423</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -986,7 +991,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 289908H</t>
+          <t>Gst Fyndnr 289916H</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91281658</v>
+        <v>91281635</v>
       </c>
       <c r="B5" t="n">
-        <v>98682</v>
+        <v>99142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623303</v>
+        <v>623297</v>
       </c>
       <c r="R5" t="n">
-        <v>6727248</v>
+        <v>6727197</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1092,12 +1097,12 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Skog, blandskog, 40-årig fuktig tallskog m björkunderväxt</t>
+          <t>Skog, blandskog, 30årig tall med björk, prunkande örtflora</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 289881N</t>
+          <t>Gst Fyndnr 289904N</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1119,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91281647</v>
+        <v>91281658</v>
       </c>
       <c r="B6" t="n">
-        <v>98681</v>
+        <v>99142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623297</v>
+        <v>623303</v>
       </c>
       <c r="R6" t="n">
-        <v>6727197</v>
+        <v>6727248</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,12 +1208,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Skog, blandskog, 30årig tall med björk, prunkande örtflora</t>
+          <t>Skog, blandskog, 40-årig fuktig tallskog m björkunderväxt</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 289892N</t>
+          <t>Gst Fyndnr 289881N</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1230,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91281621</v>
+        <v>98181692</v>
       </c>
       <c r="B7" t="n">
-        <v>97576</v>
+        <v>99142</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,37 +1246,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221063</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bomhus, Storhagen 1 km S, Gstr</t>
+          <t>Storhagen, 1 km N om dammen i Storhagen, på fastigh 16:18, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623302</v>
+        <v>623313</v>
       </c>
       <c r="R7" t="n">
-        <v>6727326</v>
+        <v>6727231</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,12 +1300,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2006-06-03</t>
+          <t>1991-08-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2006-06-03</t>
+          <t>1991-08-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,12 +1319,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Källa, källstråk i myr artad tallskog</t>
+          <t>Källa, i fuktig gles tallskog på torvmark. Utströmningsområdeför kalkrikt grundvatten.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 289917H</t>
+          <t>Gst Fyndnr 42787H</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1341,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91281622</v>
+        <v>91281647</v>
       </c>
       <c r="B8" t="n">
-        <v>98682</v>
+        <v>99141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,34 +1357,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bomhus, Storhagen 1 km S, Gstr</t>
+          <t>Bomhus, Storhagen, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623302</v>
+        <v>623297</v>
       </c>
       <c r="R8" t="n">
-        <v>6727326</v>
+        <v>6727197</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1425,12 +1430,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Källa, källstråk i myr artad tallskog</t>
+          <t>Skog, blandskog, 30årig tall med björk, prunkande örtflora</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 289916H</t>
+          <t>Gst Fyndnr 289892N</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1452,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>91281634</v>
+        <v>91281659</v>
       </c>
       <c r="B9" t="n">
-        <v>100847</v>
+        <v>99141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623297</v>
+        <v>623303</v>
       </c>
       <c r="R9" t="n">
-        <v>6727197</v>
+        <v>6727248</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1536,12 +1541,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Skog, blandskog, 30årig tall med björk, prunkande örtflora</t>
+          <t>Skog, blandskog, 40-årig fuktig tallskog m björkunderväxt</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 289905N</t>
+          <t>Gst Fyndnr 289880N</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1563,32 +1568,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>91281633</v>
+        <v>91281621</v>
       </c>
       <c r="B10" t="n">
-        <v>100383</v>
+        <v>98030</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1256</v>
+        <v>221063</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Forselles</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1652,7 +1657,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 289906H</t>
+          <t>Gst Fyndnr 289917H</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1674,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>91281644</v>
+        <v>94511452</v>
       </c>
       <c r="B11" t="n">
-        <v>101752</v>
+        <v>98030</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,37 +1690,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221235</v>
+        <v>221063</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bomhus, Storhagen, Gstr</t>
+          <t>GÄVLE, 1 km S STORHAGEN, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623297</v>
+        <v>623313</v>
       </c>
       <c r="R11" t="n">
-        <v>6727197</v>
+        <v>6727231</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1739,12 +1744,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2006-06-03</t>
+          <t>1988-05-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2006-06-03</t>
+          <t>1988-05-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>täml. rikligt med EQUI SCI. Rätt ordinär flora för övrigt. I källan växerGalium odoratum !</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,12 +1768,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Skog, blandskog, 30årig tall med björk, prunkande örtflora</t>
+          <t>Myr, kärr, tallmosse, påverkad av kalkhaltigt källvatten från en källa som mynnar ovan myren</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 289895N</t>
+          <t>Gst Fyndnr 14701H</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1785,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>94511452</v>
+        <v>98196132</v>
       </c>
       <c r="B12" t="n">
-        <v>97576</v>
+        <v>106244</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,34 +1806,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221063</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>GÄVLE, 1 km S STORHAGEN, Gstr</t>
+          <t>Bomhus, Storhagen 1 km S., Gstr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623313</v>
+        <v>623311</v>
       </c>
       <c r="R12" t="n">
-        <v>6727231</v>
+        <v>6727331</v>
       </c>
       <c r="S12" t="n">
         <v>100</v>
@@ -1850,17 +1860,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1988-05-12</t>
+          <t>1991-09-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1988-05-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>täml. rikligt med EQUI SCI. Rätt ordinär flora för övrigt. I källan växerGalium odoratum !</t>
+          <t>1991-09-24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,12 +1879,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Myr, kärr, tallmosse, påverkad av kalkhaltigt källvatten från en källa som mynnar ovan myren</t>
+          <t>skog, Tallskog, av torr-frisk lingon-blåbärstyp, flack moränm, i en gallrad tidigare överslut yta utan slutet mosstäcke.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 14701H</t>
+          <t>Gst Fyndnr 46606N</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1901,48 +1906,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>98181694</v>
+        <v>91281644</v>
       </c>
       <c r="B13" t="n">
-        <v>105807</v>
+        <v>102241</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221423</v>
+        <v>221235</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storhagen, 1 km N om dammen i Storhagen, på fastigh 16:18, Gstr</t>
+          <t>Bomhus, Storhagen, Gstr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623313</v>
+        <v>623297</v>
       </c>
       <c r="R13" t="n">
-        <v>6727231</v>
+        <v>6727197</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,12 +1971,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1991-08-24</t>
+          <t>2006-06-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1991-08-24</t>
+          <t>2006-06-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,12 +1990,12 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Källa, i fuktig gles tallskog på torvmark. Utströmningsområdeför kalkrikt grundvatten.</t>
+          <t>Skog, blandskog, 30årig tall med björk, prunkande örtflora</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 42785H</t>
+          <t>Gst Fyndnr 289895N</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2012,10 +2017,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>98181692</v>
+        <v>91281631</v>
       </c>
       <c r="B14" t="n">
-        <v>98682</v>
+        <v>106329</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,37 +2028,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>221423</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storhagen, 1 km N om dammen i Storhagen, på fastigh 16:18, Gstr</t>
+          <t>Bomhus, Storhagen 1 km S, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623313</v>
+        <v>623302</v>
       </c>
       <c r="R14" t="n">
-        <v>6727231</v>
+        <v>6727326</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2077,12 +2082,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>1991-08-24</t>
+          <t>2006-06-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1991-08-24</t>
+          <t>2006-06-03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,12 +2101,12 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Källa, i fuktig gles tallskog på torvmark. Utströmningsområdeför kalkrikt grundvatten.</t>
+          <t>Källa, källstråk i myr artad tallskog</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 42787H</t>
+          <t>Gst Fyndnr 289908H</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2123,32 +2128,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>98181688</v>
+        <v>98181694</v>
       </c>
       <c r="B15" t="n">
-        <v>100383</v>
+        <v>106329</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1256</v>
+        <v>221423</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Forselles</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2196,11 +2201,6 @@
           <t>1991-08-24</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Över 100 blommande strån av storgröe.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 42791H</t>
+          <t>Gst Fyndnr 42785H</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2239,10 +2239,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>98196132</v>
+        <v>98196135</v>
       </c>
       <c r="B16" t="n">
-        <v>105722</v>
+        <v>97983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,21 +2250,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 46606N</t>
+          <t>Gst Fyndnr 46603N</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>98196135</v>
+        <v>91281634</v>
       </c>
       <c r="B17" t="n">
-        <v>97530</v>
+        <v>101326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2361,37 +2361,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bomhus, Storhagen 1 km S., Gstr</t>
+          <t>Bomhus, Storhagen, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623311</v>
+        <v>623297</v>
       </c>
       <c r="R17" t="n">
-        <v>6727331</v>
+        <v>6727197</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2415,12 +2415,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>1991-09-24</t>
+          <t>2006-06-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1991-09-24</t>
+          <t>2006-06-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>skog, Tallskog, av torr-frisk lingon-blåbärstyp, flack moränm, i en gallrad tidigare överslut yta utan slutet mosstäcke.</t>
+          <t>Skog, blandskog, 30årig tall med björk, prunkande örtflora</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 46603N</t>
+          <t>Gst Fyndnr 289905N</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 19899-2026 artfynd.xlsx
+++ b/artfynd/A 19899-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91281633</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98181688</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91281622</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91281635</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91281658</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98181692</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91281647</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1565,6 +1605,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91281659</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1676,6 +1721,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91281621</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94511452</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1903,6 +1958,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98196132</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2014,6 +2074,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91281644</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2125,6 +2190,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91281631</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2236,6 +2306,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98181694</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2347,6 +2422,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98196135</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2458,8 +2538,31 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91281634</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>